--- a/registration_forms/029_piano_festival_registration_form--registration_forms.xlsx
+++ b/registration_forms/029_piano_festival_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>piano_festival_registration_form_name</t>
+          <t>participant_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Piano Festival Registration Form Name</t>
+          <t>Participant Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>participant_name</t>
+          <t>participant_contact_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>participant_name</t>
+          <t>Participant Contact Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_contact_details</t>
+          <t>participant_description</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>participant_contact_details</t>
+          <t>Participant Description</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>piano_festival_registration_form_description</t>
+          <t>participant_phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>piano_festival_registration_form_description</t>
+          <t>Participant Phone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>piano_festival_registration_form_description</t>
+          <t>participant_email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>piano_festival_registration_form_description</t>
+          <t>Participant Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,269 +635,131 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>participant_phone</t>
+          <t>participant_notes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>participant_phone</t>
+          <t>Participant Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>participant_email</t>
+          <t>participant_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>participant_email</t>
+          <t>Participant Status</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>participant_notes</t>
+          <t>participant_registration_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>participant_notes</t>
+          <t>Participant Registration Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>piano_festival_participant_status</t>
+          <t>participant_last_seen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>piano_festival_participant_status</t>
+          <t>Participant Last Seen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>piano_festival_participant_status</t>
+          <t>piano_festival_participant_id</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>piano_festival_participant_status</t>
+          <t>Piano Festival Participant ID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_status</t>
+          <t>participant_status_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>participant_status</t>
+          <t>Participant Status 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>participant_registration_date</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>participant_registration_date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>participant_last_seen</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>participant_last_seen</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>piano_festival_participant_id</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>piano_festival_participant_id</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>piano_festival_participant_status</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>piano_festival_participant_status</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>participant_last_seen</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>participant_last_seen</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>piano_festival_participant_status</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>piano_festival_participant_status</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -914,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -964,216 +826,97 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Phone', 'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>piano_festival_participant_status_choices</t>
+          <t>participant_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'confirmed',_'value':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Confirmed', 'value': 'Confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>piano_festival_participant_status_choices</t>
+          <t>participant_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>piano_festival_participant_status_choices</t>
+          <t>participant_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'not_confirmed',_'value':_'not_confirmed'}</t>
+          <t>not_confirmed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Not confirmed', 'value': 'Not confirmed'}</t>
+          <t>Not confirmed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>piano_festival_participant_status_choices</t>
+          <t>participant_status_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'confirmed',_'value':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Confirmed', 'value': 'Confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>piano_festival_participant_status_choices</t>
+          <t>participant_status_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'pending',_'value':_'pending'}</t>
+          <t>not_confirmed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Pending', 'value': 'Pending'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>participant_status_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_9,_'label':_'confirmed',_'value':_'confirmed'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 9, 'label': 'Confirmed', 'value': 'Confirmed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>participant_status_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_10,_'label':_'pending',_'value':_'pending'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 10, 'label': 'Pending', 'value': 'Pending'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>participant_status_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_11,_'label':_'not_confirmed',_'value':_'not_confirmed'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 11, 'label': 'Not confirmed', 'value': 'Not confirmed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>piano_festival_participant_status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_15,_'label':_'confirmed',_'value':_'confirmed'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 15, 'label': 'Confirmed', 'value': 'Confirmed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>piano_festival_participant_status_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_16,_'label':_'not_confirmed',_'value':_'not_confirmed'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 16, 'label': 'Not confirmed', 'value': 'Not confirmed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>piano_festival_participant_status_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_15,_'label':_'confirmed',_'value':_'confirmed'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 15, 'label': 'Confirmed', 'value': 'Confirmed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>piano_festival_participant_status_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_16,_'label':_'not_confirmed',_'value':_'not_confirmed'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 16, 'label': 'Not confirmed', 'value': 'Not confirmed'}</t>
+          <t>Not confirmed</t>
         </is>
       </c>
     </row>
